--- a/Sheet_ATruong/Duong_Tat_Truong.xlsx
+++ b/Sheet_ATruong/Duong_Tat_Truong.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="257">
   <si>
     <t>BÁO CÁO BÀI TẬP DỰ ÁN NHÓM MÔN ĐẢM BẢO CHẤT LƯỢNG PHẦN MỀM</t>
   </si>
@@ -793,6 +793,9 @@
 → hệ thống không có rule nào đánh giá mật khẩu</t>
   </si>
   <si>
+    <t>Không cần Fix vì là kiểm thử hộp đen</t>
+  </si>
+  <si>
     <t>medium</t>
   </si>
   <si>
@@ -827,9 +830,6 @@
   </si>
   <si>
     <t>Không có chức năng trong hệ thống</t>
-  </si>
-  <si>
-    <t>Thêm chức năng Search</t>
   </si>
   <si>
     <t>High</t>
@@ -1685,7 +1685,7 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1750,12 +1750,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2835,124 +2829,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="29" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="B16" s="32"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="30"/>
+      <c r="C16" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34" t="s">
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="36"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="34"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="34" t="s">
+      <c r="D17" s="37"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="41"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
-      <c r="T17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="39"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
     </row>
     <row r="18" spans="1:20">
-      <c r="B18" s="37"/>
-      <c r="C18" s="33" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="42" t="s">
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
     </row>
     <row r="19" spans="1:20">
-      <c r="B19" s="37"/>
-      <c r="C19" s="60" t="s">
+      <c r="B19" s="35"/>
+      <c r="C19" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34" t="s">
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="37"/>
-    </row>
-    <row r="20" s="28" customFormat="1" spans="1:20">
-      <c r="A20" s="28" t="s">
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+    </row>
+    <row r="20" s="26" customFormat="1" spans="1:20">
+      <c r="A20" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="28" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2996,96 +2990,96 @@
       </c>
     </row>
     <row r="24" spans="1:20">
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="59" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="40"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="38"/>
     </row>
     <row r="25" spans="1:20">
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="43" t="s">
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="40"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="38"/>
     </row>
     <row r="26" spans="1:20">
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="43" t="s">
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="40"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
       <c r="K26"/>
       <c r="L26"/>
     </row>
     <row r="27" spans="1:20">
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="43" t="s">
+      <c r="D27" s="43"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="40"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="38"/>
     </row>
     <row r="28" spans="1:20">
-      <c r="C28" s="47"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49" t="s">
+      <c r="C28" s="45"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="51"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="49"/>
     </row>
     <row r="29" spans="1:20">
-      <c r="C29" s="47"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="43" t="s">
+      <c r="C29" s="45"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="38"/>
     </row>
     <row r="30" spans="1:20">
-      <c r="C30" s="52"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="43" t="s">
+      <c r="C30" s="50"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="38"/>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
@@ -3096,90 +3090,90 @@
       </c>
     </row>
     <row r="32" spans="1:20">
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="43" t="s">
+      <c r="D32" s="43"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="40"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="38"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="C33" s="47"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="43" t="s">
+      <c r="C33" s="45"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="40"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="38"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="C34" s="52"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="43" t="s">
+      <c r="C34" s="50"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="40"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="38"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="45"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="43" t="s">
+      <c r="D35" s="43"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="40"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="38"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="C36" s="47"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="43" t="s">
+      <c r="C36" s="45"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="40"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="C37" s="52"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="43" t="s">
+      <c r="C37" s="50"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="40"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="38"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
@@ -3190,58 +3184,58 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="38"/>
       <c r="F39" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="G39" s="53"/>
-      <c r="H39" s="54"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="52"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="C40" s="62" t="s">
+      <c r="C40" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="45"/>
-      <c r="E40" s="46"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="44"/>
       <c r="F40" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="G40" s="53"/>
-      <c r="H40" s="54"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="52"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="C41" s="47"/>
-      <c r="E41" s="48"/>
+      <c r="C41" s="45"/>
+      <c r="E41" s="46"/>
       <c r="F41" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G41" s="53"/>
-      <c r="H41" s="54"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="52"/>
       <c r="J41"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="C42" s="47"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="44" t="s">
+      <c r="C42" s="45"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="G42" s="39"/>
-      <c r="H42" s="54"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="52"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="C43" s="52"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="51"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="49"/>
       <c r="F43" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="53"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="55"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="53"/>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
@@ -3252,19 +3246,19 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="59" t="s">
         <v>50</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18"/>
-      <c r="F45" s="43" t="s">
+      <c r="F45" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="G45" s="39"/>
-      <c r="H45" s="40"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="C46" s="61" t="s">
+      <c r="C46" s="59" t="s">
         <v>52</v>
       </c>
       <c r="D46" s="18"/>
@@ -3272,20 +3266,20 @@
       <c r="F46" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G46" s="53"/>
-      <c r="H46" s="54"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="52"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="C47" s="62" t="s">
+      <c r="C47" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="40"/>
-      <c r="F47" s="43" t="s">
+      <c r="D47" s="37"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="G47" s="39"/>
-      <c r="H47" s="40"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="38"/>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
@@ -3296,16 +3290,16 @@
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="43" t="s">
+      <c r="D49" s="37"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="G49" s="39"/>
-      <c r="H49" s="40"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="38"/>
     </row>
     <row r="50" spans="1:9">
       <c r="C50" s="18" t="s">
@@ -3313,23 +3307,23 @@
       </c>
       <c r="D50" s="18"/>
       <c r="E50" s="18"/>
-      <c r="F50" s="43" t="s">
+      <c r="F50" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="G50" s="39"/>
-      <c r="H50" s="40"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="38"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="C51" s="43" t="s">
+      <c r="C51" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="39"/>
-      <c r="E51" s="40"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="38"/>
       <c r="F51" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G51" s="53"/>
-      <c r="H51" s="54"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="52"/>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
@@ -3340,36 +3334,36 @@
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="C53" s="43" t="s">
+      <c r="C53" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="39"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="43" t="s">
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="40"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="38"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="39"/>
-      <c r="E54" s="40"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="38"/>
       <c r="F54" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G54" s="53"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="54"/>
+      <c r="G54" s="51"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="52"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="26" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3430,10 +3424,10 @@
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="28" t="s">
+      <c r="B63" s="26" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3453,16 +3447,16 @@
       </c>
     </row>
     <row r="67" ht="17.1" customHeight="1" spans="1:13">
-      <c r="D67" s="57" t="s">
+      <c r="D67" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="E67" s="57" t="s">
+      <c r="E67" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="F67" s="57" t="s">
+      <c r="F67" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="G67" s="58" t="s">
+      <c r="G67" s="56" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3501,7 +3495,7 @@
       <c r="E70" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="F70" s="64" t="s">
+      <c r="F70" s="62" t="s">
         <v>95</v>
       </c>
       <c r="G70" s="18" t="s">
@@ -3517,34 +3511,34 @@
       </c>
     </row>
     <row r="72" ht="65.1" customHeight="1" spans="1:13">
-      <c r="D72" s="59" t="s">
+      <c r="D72" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="E72" s="59" t="s">
+      <c r="E72" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="F72" s="59" t="s">
+      <c r="F72" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="G72" s="59" t="s">
+      <c r="G72" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="H72" s="59" t="s">
+      <c r="H72" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="I72" s="59" t="s">
+      <c r="I72" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="J72" s="59" t="s">
+      <c r="J72" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="K72" s="59" t="s">
+      <c r="K72" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="L72" s="59" t="s">
+      <c r="L72" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="M72" s="59" t="s">
+      <c r="M72" s="57" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3710,7 +3704,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="8"/>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="63" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3720,7 +3714,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="63" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4580,74 +4574,76 @@
       <c r="H62" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="I62" s="23" t="s">
+      <c r="I62" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="J62" s="24"/>
-      <c r="K62" s="25" t="s">
+      <c r="J62" s="21" t="s">
         <v>243</v>
+      </c>
+      <c r="K62" s="23" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1" spans="1:11">
       <c r="C63" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>237</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>148</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>158</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K63" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" ht="57" customHeight="1" spans="1:11">
       <c r="C64" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>237</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="K64" s="18" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="65" spans="5:10">
-      <c r="E65" s="26"/>
+      <c r="E65" s="24"/>
       <c r="J65" s="13"/>
     </row>
     <row r="67" spans="5:10">
@@ -4657,10 +4653,10 @@
       <c r="F68"/>
     </row>
     <row r="70" spans="5:10">
-      <c r="F70" s="27"/>
+      <c r="F70" s="25"/>
     </row>
     <row r="71" spans="5:10">
-      <c r="F71" s="27"/>
+      <c r="F71" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
